--- a/Codebooks/Human Codebooks/content - cleaned/C - Content Analysis Codebook (cleaned) - Kally.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/C - Content Analysis Codebook (cleaned) - Kally.xlsx
@@ -681,7 +681,7 @@
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
@@ -708,13 +708,13 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>Men need to be equal partners, Men need to improve themselves</t>
+          <t>Men need to improve themselves, Men need to be equal partners</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr"/>
@@ -726,7 +726,7 @@
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion, Humor/satire</t>
+          <t>Commentary/opinion, Personal story, Humor/satire</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr"/>
@@ -833,13 +833,13 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>More equality/respect for men, More equality/respect for women</t>
+          <t>More equality/respect for women, More equality/respect for men</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -851,7 +851,7 @@
       <c r="U3" s="3" t="inlineStr"/>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
@@ -978,7 +978,7 @@
       <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Economic/status pressure, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Economic/status pressure</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG5" s="3" t="inlineStr"/>
@@ -1177,7 +1177,7 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Money/status, Dating/marriage, Fitness/self-improvement</t>
+          <t>Fitness/self-improvement, Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
       <c r="Q6" s="3" t="inlineStr"/>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>More wealth/status, More self-discipline/fitness</t>
+          <t>More self-discipline/fitness, More wealth/status</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms, Calls for women to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG6" s="3" t="inlineStr"/>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Humor or sarcasm, Shares something surprising</t>
+          <t>Shares something surprising, Humor or sarcasm</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
@@ -1337,13 +1337,13 @@
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Global political/social/cultural problems, Men’s behavior</t>
+          <t>Global political/social/cultural problems, Men's behavior</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>More self-discipline/fitness, More emotional growth/healing</t>
+          <t>More emotional growth/healing, More self-discipline/fitness</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>Calls for audience to share the content</t>
+          <t>Calls for audience to share content</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms, Calls for women to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr"/>
@@ -1815,7 +1815,7 @@
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Status seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism, Status seeking</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>@thesheilaojei I’m a provider who believes that equal rights equates to equal responsibilities</t>
+          <t>@thesheilaojei I'm a provider who believes that equal rights equates to equal responsibilities</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1934,7 +1934,7 @@
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>I’m not perfect… only trying to be a decent human, husband lover, present father, supportive sibling, inspiring colleague, and good friend. So help me God</t>
+          <t>I'm not perfect… only trying to be a decent human, husband lover, present father, supportive sibling, inspiring colleague, and good friend. So help me God</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -2041,7 +2041,7 @@
       <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
@@ -2228,7 +2228,7 @@
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Social issues, e.g. corruption, Money/status, Mental health</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Mental health, Money/status</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
@@ -2255,19 +2255,19 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Men are disadvantaged/victims, Men need to be emotionally open</t>
+          <t>Men need to be emotionally open, Men are disadvantaged/victims</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>Kenyan or Nigerian political/social problems, Men’s behavior, Economic/status pressure, Mental health/emotional struggle</t>
+          <t>Kenyan or Nigerian political/social problems, Mental health/emotional struggle, Economic/status pressure, Men's behavior</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr"/>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>Social or political change, More emotional growth/healing, More equality/respect for men</t>
+          <t>More emotional growth/healing, More equality/respect for men, Social or political change</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -2279,7 +2279,7 @@
       <c r="U15" s="3" t="inlineStr"/>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr"/>
@@ -2372,13 +2372,13 @@
       <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr"/>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>More self-discipline/fitness, More emotional growth/healing</t>
+          <t>More emotional growth/healing, More self-discipline/fitness</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Money/status, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
@@ -2501,13 +2501,13 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to provide/succeed</t>
+          <t>Men need to provide/succeed, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Economic/status pressure</t>
+          <t>Economic/status pressure, Men's behavior</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr"/>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Friends/socializing</t>
+          <t>Friends/socializing, Dating/marriage</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
@@ -2628,13 +2628,13 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to not show emotions</t>
+          <t>Men need to not show emotions, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr"/>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Men''s behavior, Global political/social/cultural problems</t>
+          <t>Global political/social/cultural problems, Men's behavior</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr"/>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr"/>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr"/>
@@ -2867,7 +2867,7 @@
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality, Fitness/self-improvement</t>
+          <t>Gender issues, e.g. equality, Fitness/self-improvement, Dating/marriage</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
@@ -2894,19 +2894,19 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to not show emotions, Men need to improve themselves</t>
+          <t>Men need to improve themselves, Men need to not show emotions, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>Men''s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr"/>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More self-discipline/fitness</t>
+          <t>More self-discipline/fitness, Assert dominance/control</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr"/>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality, Money/status</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AF21" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG21" s="3" t="inlineStr"/>
@@ -3156,13 +3156,13 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>Men need to not show emotions, Men need to improve themselves</t>
+          <t>Men need to improve themselves, Men need to not show emotions</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr"/>
@@ -3180,7 +3180,7 @@
       <c r="U22" s="3" t="inlineStr"/>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
@@ -3260,7 +3260,7 @@
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality, Religion/morality</t>
+          <t>Gender issues, e.g. equality, Religion/morality, Dating/marriage</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
@@ -3293,7 +3293,7 @@
       <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr"/>
@@ -3383,7 +3383,7 @@
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality, Religion/morality</t>
+          <t>Gender issues, e.g. equality, Religion/morality, Dating/marriage</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr"/>
@@ -3416,7 +3416,7 @@
       <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr"/>
@@ -3434,7 +3434,7 @@
       <c r="U24" s="3" t="inlineStr"/>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Connection/social interaction</t>
+          <t>Connection/social interaction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
@@ -3506,7 +3506,7 @@
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Mental health, Religion/morality</t>
+          <t>Religion/morality, Dating/marriage, Mental health</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
@@ -3539,7 +3539,7 @@
       <c r="O25" s="3" t="inlineStr"/>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr"/>
@@ -3557,7 +3557,7 @@
       <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Connection/social interaction</t>
+          <t>Connection/social interaction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Money/status, Dating/marriage</t>
+          <t>Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr"/>
@@ -3652,13 +3652,13 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>Men need to provide/succeed, Men need to improve themselves, Men need to be fully self-reliant</t>
+          <t>Men need to be fully self-reliant, Men need to improve themselves, Men need to provide/succeed</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr"/>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Economic/status pressure</t>
+          <t>Economic/status pressure, Men's behavior</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr"/>
@@ -3676,7 +3676,7 @@
       <c r="U26" s="3" t="inlineStr"/>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr"/>
@@ -3752,7 +3752,7 @@
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Money/status, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
@@ -3785,7 +3785,7 @@
       <c r="O27" s="3" t="inlineStr"/>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Economic/status pressure, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Economic/status pressure, Women/feminism</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr"/>
@@ -3803,7 +3803,7 @@
       <c r="U27" s="3" t="inlineStr"/>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Connection/social interaction</t>
+          <t>Connection/social interaction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
@@ -3912,7 +3912,7 @@
       <c r="O28" s="3" t="inlineStr"/>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr"/>
@@ -3930,7 +3930,7 @@
       <c r="U28" s="3" t="inlineStr"/>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Connection/social interaction</t>
+          <t>Connection/social interaction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
@@ -4010,7 +4010,7 @@
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Religion/morality</t>
+          <t>Religion/morality, Dating/marriage</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr"/>
@@ -4065,7 +4065,7 @@
       <c r="U29" s="3" t="inlineStr"/>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Connection/social interaction</t>
+          <t>Connection/social interaction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
@@ -4145,7 +4145,7 @@
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Money/status, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr"/>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>Men need to provide/succeed, Men need to improve themselves, Men need to not show emotions</t>
+          <t>Men need to improve themselves, Men need to not show emotions, Men need to provide/succeed</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr"/>
@@ -4184,7 +4184,7 @@
       <c r="Q30" s="3" t="inlineStr"/>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More self-discipline/fitness</t>
+          <t>More self-discipline/fitness, Assert dominance/control</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -4196,7 +4196,7 @@
       <c r="U30" s="3" t="inlineStr"/>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr"/>
@@ -4299,13 +4299,13 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>Men need to provide/succeed, Men are disadvantaged/victims</t>
+          <t>Men are disadvantaged/victims, Men need to provide/succeed</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr"/>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>Economic/status pressure, Mental health/emotional struggle, Men's behavior</t>
+          <t>Mental health/emotional struggle, Economic/status pressure, Men's behavior</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr"/>
@@ -4323,7 +4323,7 @@
       <c r="U31" s="3" t="inlineStr"/>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction, Information seeking</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr"/>
@@ -4399,7 +4399,7 @@
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr"/>
@@ -4426,19 +4426,19 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to not show emotions, Men need to improve themselves</t>
+          <t>Men need to improve themselves, Men need to not show emotions, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr"/>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More self-discipline/fitness</t>
+          <t>More self-discipline/fitness, Assert dominance/control</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -4551,7 +4551,7 @@
       <c r="O33" s="3" t="inlineStr"/>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr"/>
@@ -4573,7 +4573,7 @@
       <c r="U33" s="3" t="inlineStr"/>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction, Information seeking</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr"/>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Shares something surprising, Others</t>
+          <t>Shares something surprising, Other</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -4784,7 +4784,7 @@
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Friends/socializing</t>
+          <t>Friends/socializing, Dating/marriage</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
@@ -4817,13 +4817,13 @@
       <c r="O35" s="3" t="inlineStr"/>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Women/feminism</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr"/>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More self-discipline/fitness</t>
+          <t>More self-discipline/fitness, Assert dominance/control</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr"/>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Shares something surprising, Others</t>
+          <t>Shares something surprising, Other</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Gender issues, e.g. equality, Religion/morality, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Religion/morality, Family/children</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
@@ -4948,7 +4948,7 @@
       <c r="O36" s="3" t="inlineStr"/>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>Global political/social/cultural problems, Women/feminism, Mental health/emotional struggle</t>
+          <t>Global political/social/cultural problems, Mental health/emotional struggle, Women/feminism</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr"/>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>Calls for women to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr"/>
@@ -5036,13 +5036,13 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Compelling question, Uses a news headline or social media trend as opener</t>
+          <t>Uses a news headline or social media trend as opener, Compelling question</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Dating/marriage</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr"/>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
@@ -5304,7 +5304,7 @@
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Mental health, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Mental health</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>Men need to be equal partners, Men need to be emotionally open, Men need to improve themselves</t>
+          <t>Men need to be emotionally open, Men need to improve themselves, Men need to be equal partners</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr"/>
@@ -5349,13 +5349,13 @@
       <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Advice/instruction, Commentary/opinion</t>
+          <t>Advice/instruction, Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr"/>
@@ -5554,7 +5554,7 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Gender issues, e.g. equality, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Family/children</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
@@ -5599,13 +5599,13 @@
       <c r="S41" s="3" t="inlineStr"/>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr"/>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction, Information seeking</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
@@ -5926,7 +5926,7 @@
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr"/>
@@ -5938,13 +5938,13 @@
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="AF2" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -6053,25 +6053,25 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>More emotional growth/healing, More equality/respect for women</t>
+          <t>More equality/respect for women, More emotional growth/healing</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr"/>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr"/>
@@ -6147,7 +6147,7 @@
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Mental health, Family/children</t>
+          <t>Gender issues, e.g. equality, Family/children, Mental health</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
@@ -6174,31 +6174,31 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Men need to improve themselves, Men need to be emotionally open, Men need to provide/succeed</t>
+          <t>Men need to be emotionally open, Men need to improve themselves, Men need to provide/succeed</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>More self-discipline/fitness, More emotional growth/healing, Building community</t>
+          <t>More emotional growth/healing, More self-discipline/fitness, Building community</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Motivational speech</t>
+          <t>Motivational speech, Personal story</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -6381,7 +6381,7 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Mental health, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Mental health</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
@@ -6414,7 +6414,7 @@
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle, Kenyan or Nigerian political/social problems, Global political/social/cultural problems</t>
+          <t>Kenyan or Nigerian political/social problems, Global political/social/cultural problems, Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr"/>
@@ -6432,7 +6432,7 @@
       <c r="U6" s="3" t="inlineStr"/>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
@@ -6498,13 +6498,13 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Shares something surprising, Shares something violent or gross</t>
+          <t>Shares something violent or gross, Shares something surprising</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Social issues, e.g. corruption, Mental health, Family/children</t>
+          <t>Social issues, e.g. corruption, Family/children, Mental health</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
@@ -6543,7 +6543,7 @@
       <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
@@ -6609,13 +6609,13 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Shares something surprising, Shares something violent or gross</t>
+          <t>Shares something violent or gross, Shares something surprising</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Family/children</t>
+          <t>Family/children, Mental health</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
@@ -6648,7 +6648,7 @@
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr"/>
@@ -6666,7 +6666,7 @@
       <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
@@ -6738,7 +6738,7 @@
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Friends/socializing, Religion/morality</t>
+          <t>Friends/socializing, Religion/morality, Mental health</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
@@ -6771,7 +6771,7 @@
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
+          <t>Kenyan or Nigerian political/social problems, Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr"/>
@@ -6783,13 +6783,13 @@
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr"/>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
@@ -6861,7 +6861,7 @@
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Mental health, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Mental health</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
@@ -6894,7 +6894,7 @@
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
+          <t>Kenyan or Nigerian political/social problems, Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr"/>
@@ -6912,7 +6912,7 @@
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr"/>
@@ -6988,7 +6988,7 @@
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Mental health, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Mental health</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
@@ -7021,7 +7021,7 @@
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle, Kenyan or Nigerian political/social problems, Global political/social/cultural problems</t>
+          <t>Kenyan or Nigerian political/social problems, Global political/social/cultural problems, Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr"/>
@@ -7039,7 +7039,7 @@
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
@@ -7105,13 +7105,13 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Shares something surprising, Shares something violent or gross</t>
+          <t>Shares something violent or gross, Shares something surprising</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Family/children, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Family/children</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr"/>
@@ -7353,7 +7353,7 @@
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Family/children, Dating/marriage</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Family/children</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
@@ -7499,31 +7499,31 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Men need to improve themselves, Men need to be emotionally open</t>
+          <t>Men need to be emotionally open, Men need to improve themselves</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>Kenyan or Nigerian political/social problems, Women/feminism, Men’s behavior</t>
+          <t>Kenyan or Nigerian political/social problems, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr"/>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>More emotional growth/healing, Building community, Social or political change</t>
+          <t>More emotional growth/healing, Social or political change, Building community</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, Motivational speech</t>
+          <t>Motivational speech, Advice/instruction</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr"/>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr"/>
@@ -7595,7 +7595,7 @@
       <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Family/children</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
@@ -7646,7 +7646,7 @@
       <c r="U16" s="3" t="inlineStr"/>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
@@ -7718,7 +7718,7 @@
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Family/children</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
@@ -7751,7 +7751,7 @@
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr"/>
@@ -7763,7 +7763,7 @@
       <c r="S17" s="3" t="inlineStr"/>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction, Personal story</t>
+          <t>Advice/instruction, Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr"/>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Calls for women to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr"/>
@@ -7845,7 +7845,7 @@
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Family/children, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Family/children</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
@@ -7878,7 +7878,7 @@
       <c r="O18" s="3" t="inlineStr"/>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Kenyan or Nigerian political/social problems, Women/feminism, Men’s behavior</t>
+          <t>Kenyan or Nigerian political/social problems, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr"/>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr"/>
@@ -7972,7 +7972,7 @@
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Family/children, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Family/children</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
@@ -7999,13 +7999,13 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to provide/succeed</t>
+          <t>Men need to provide/succeed, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>Kenyan or Nigerian political/social problems, Global political/social/cultural problems, Western political/social influence, Women/feminism, Men’s behavior</t>
+          <t>Kenyan or Nigerian political/social problems, Global political/social/cultural problems, Western political/social influence, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr"/>
@@ -8017,7 +8017,7 @@
       <c r="S19" s="3" t="inlineStr"/>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr"/>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr"/>
@@ -8099,7 +8099,7 @@
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
@@ -8126,13 +8126,13 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to be fully self-reliant, Men are disadvantaged/victims</t>
+          <t>Men need to be fully self-reliant, Men are disadvantaged/victims, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr"/>
@@ -8144,13 +8144,13 @@
       <c r="S20" s="3" t="inlineStr"/>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr"/>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr"/>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr"/>
@@ -8275,7 +8275,7 @@
       <c r="S21" s="3" t="inlineStr"/>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr"/>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="AF21" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG21" s="3" t="inlineStr"/>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Shares something surprising, Humor or sarcasm, Compelling question</t>
+          <t>Shares something surprising, Compelling question, Humor or sarcasm</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
@@ -8398,7 +8398,7 @@
       <c r="S22" s="3" t="inlineStr"/>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction, Humor/satire</t>
+          <t>Advice/instruction, Commentary/opinion, Humor/satire</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr"/>
@@ -8509,7 +8509,7 @@
       <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior, Economic/status pressure</t>
+          <t>Economic/status pressure, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr"/>
@@ -8521,13 +8521,13 @@
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr"/>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -8632,7 +8632,7 @@
       <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr"/>
@@ -8644,13 +8644,13 @@
       <c r="S24" s="3" t="inlineStr"/>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr"/>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
@@ -8749,25 +8749,25 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to be fully self-reliant, Men are disadvantaged/victims</t>
+          <t>Men need to be fully self-reliant, Men are disadvantaged/victims, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr"/>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr"/>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More equality/respect for men</t>
+          <t>More equality/respect for men, Assert dominance/control</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, Motivational speech</t>
+          <t>Motivational speech, Advice/instruction</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr"/>
@@ -8886,25 +8886,25 @@
       <c r="O26" s="3" t="inlineStr"/>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr"/>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More self-discipline/fitness, More equality/respect for men</t>
+          <t>More equality/respect for men, More self-discipline/fitness, Assert dominance/control</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, Motivational speech</t>
+          <t>Motivational speech, Advice/instruction</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr"/>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>Self expression/identity construction, Status seeking, Information seeking</t>
+          <t>Self expression/identity construction, Information seeking, Status seeking</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr"/>
@@ -9013,7 +9013,7 @@
       <c r="O27" s="3" t="inlineStr"/>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr"/>
@@ -9025,13 +9025,13 @@
       <c r="S27" s="3" t="inlineStr"/>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, Motivational speech, Commentary/opinion</t>
+          <t>Motivational speech, Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr"/>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>Self expression/identity construction, Status seeking, Information seeking</t>
+          <t>Self expression/identity construction, Information seeking, Status seeking</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr"/>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Compelling question, Shares something surprising, Uses a news headline or social media trend as opener</t>
+          <t>Uses a news headline or social media trend as opener, Shares something surprising, Compelling question</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr"/>
@@ -9113,7 +9113,7 @@
       <c r="H28" s="3" t="inlineStr"/>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
@@ -9140,40 +9140,40 @@
       <c r="O28" s="3" t="inlineStr"/>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>Economic/status pressure, Mental health/emotional struggle, Women/feminism</t>
+          <t>Mental health/emotional struggle, Economic/status pressure, Women/feminism</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr"/>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More equality/respect for men, Other</t>
+          <t>More equality/respect for men, Assert dominance/control, Other</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>"Don't fall lin love”</t>
+          <t>"Don't fall lin love"</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, News/telling facts, Commentary/opinion</t>
+          <t>Advice/instruction, Commentary/opinion, News/telling facts</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr"/>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>Self expression/identity construction, Status seeking, Information seeking</t>
+          <t>Self expression/identity construction, Information seeking, Status seeking</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>Facts/statistics, Generalizations about men/women, Cultural/social observations</t>
+          <t>Generalizations about men/women, Cultural/social observations, Facts/statistics</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr"/>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>References data, Presented as common sense, Anecdotal examples</t>
+          <t>Presented as common sense, Anecdotal examples, References data</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr"/>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr"/>
@@ -9271,13 +9271,13 @@
       <c r="O29" s="3" t="inlineStr"/>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr"/>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More equality/respect for men, More self-discipline/fitness</t>
+          <t>More equality/respect for men, More self-discipline/fitness, Assert dominance/control</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -9289,12 +9289,12 @@
       <c r="U29" s="3" t="inlineStr"/>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Entertainment/escapism, Information seeking</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>Stories about men/women, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Stories about men/women</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr"/>
@@ -9361,7 +9361,7 @@
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Family/children, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Family/children</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr"/>
@@ -9388,19 +9388,19 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>Men need to be dominant/lead, Men are disadvantaged/victims, Men need to provide/succeed</t>
+          <t>Men are disadvantaged/victims, Men need to provide/succeed, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr"/>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr"/>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More self-discipline/fitness</t>
+          <t>More self-discipline/fitness, Assert dominance/control</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -9412,7 +9412,7 @@
       <c r="U30" s="3" t="inlineStr"/>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Entertainment/escapism, Information seeking</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr"/>
@@ -9488,7 +9488,7 @@
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Dating/marriage, Mental health, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Dating/marriage, Mental health</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to be fully self-reliant, Men need to not show emotions, Men need to improve themselves, Other</t>
+          <t>Men need to be fully self-reliant, Men need to improve themselves, Men need to not show emotions, Men need to dominate/lead, Other</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -9525,13 +9525,13 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr"/>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More self-discipline/fitness</t>
+          <t>More self-discipline/fitness, Assert dominance/control</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -9548,13 +9548,13 @@
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Stories about men/women, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Stories about men/women, Personal experience</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr"/>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense, References external sources, such as other influencers</t>
+          <t>References external sources, such as other influencers, Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
@@ -9585,7 +9585,7 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr"/>
@@ -9619,7 +9619,7 @@
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality, Family/children</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Family/children</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr"/>
@@ -9646,19 +9646,19 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men are disadvantaged/victims, Men need to not show emotions</t>
+          <t>Men are disadvantaged/victims, Men need to not show emotions, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr"/>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More equality/respect for men, More self-discipline/fitness</t>
+          <t>More equality/respect for men, More self-discipline/fitness, Assert dominance/control</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -9670,12 +9670,12 @@
       <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>Self expression/identity construction, Status seeking, Connection/social interaction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Status seeking</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about men/women, Stories about men/women, Cultural/social observations</t>
+          <t>Generalizations about men/women, Cultural/social observations, Stories about men/women</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr"/>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr"/>
@@ -9746,7 +9746,7 @@
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality, Family/children</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Family/children</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
@@ -9773,13 +9773,13 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to be fully self-reliant</t>
+          <t>Men need to be fully self-reliant, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr"/>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr"/>
@@ -9797,7 +9797,7 @@
       <c r="U33" s="3" t="inlineStr"/>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction, Connection/social interaction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Calls for women to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr"/>
@@ -9869,7 +9869,7 @@
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Dating/marriage</t>
+          <t>Dating/marriage, Mental health</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr"/>
@@ -9902,7 +9902,7 @@
       <c r="O34" s="3" t="inlineStr"/>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr"/>
@@ -9920,7 +9920,7 @@
       <c r="U34" s="3" t="inlineStr"/>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
@@ -9988,13 +9988,13 @@
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Family/children</t>
+          <t>Family/children, Mental health</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr"/>
@@ -10033,13 +10033,13 @@
       <c r="S35" s="3" t="inlineStr"/>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr"/>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
@@ -10111,7 +10111,7 @@
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
@@ -10148,13 +10148,13 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, Men's behavior, Global political/social/cultural problems</t>
+          <t>Global political/social/cultural problems, Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr"/>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>More emotional growth/healing, Building community, Social or political change</t>
+          <t>More emotional growth/healing, Social or political change, Building community</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       <c r="U36" s="3" t="inlineStr"/>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr"/>
@@ -10236,13 +10236,13 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Shares something sexual, Shares something surprising</t>
+          <t>Shares something surprising, Shares something sexual</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr"/>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to not show emotions</t>
+          <t>Men need to not show emotions, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr"/>
@@ -10281,7 +10281,7 @@
       <c r="Q37" s="3" t="inlineStr"/>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More self-discipline/fitness</t>
+          <t>More self-discipline/fitness, Assert dominance/control</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -10293,7 +10293,7 @@
       <c r="U37" s="3" t="inlineStr"/>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction, Status seeking</t>
+          <t>Self expression/identity construction, Information seeking, Status seeking</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr"/>
@@ -10410,7 +10410,7 @@
       <c r="S38" s="3" t="inlineStr"/>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>News/telling facts, Commentary/opinion</t>
+          <t>Commentary/opinion, News/telling facts</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr"/>
@@ -10521,7 +10521,7 @@
       <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Global political/social/cultural problems</t>
+          <t>Global political/social/cultural problems, Men's behavior</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr"/>
@@ -10539,7 +10539,7 @@
       <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
@@ -10607,13 +10607,13 @@
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Friends/socializing, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Friends/socializing, Mental health</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr"/>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>Men need to be emotionally open, Men need to build community</t>
+          <t>Men need to be emotionally open, Other</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr"/>
@@ -10652,13 +10652,13 @@
       <c r="S40" s="3" t="inlineStr"/>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Motivational speech, Personal story</t>
+          <t>Motivational speech, Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr"/>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr"/>
@@ -10734,7 +10734,7 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Mental health</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
@@ -10785,18 +10785,18 @@
       <c r="U41" s="3" t="inlineStr"/>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>Facts/statistics, Cultural/social observations</t>
+          <t>Cultural/social observations, Facts/statistics</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr"/>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>References data, Presented as common sense</t>
+          <t>Presented as common sense, References data</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr"/>

--- a/Codebooks/Human Codebooks/content - cleaned/C - Content Analysis Codebook (cleaned) - Kally.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/C - Content Analysis Codebook (cleaned) - Kally.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG5" s="3" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms, Calls for women to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG6" s="3" t="inlineStr"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms, Calls for women to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr"/>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr"/>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr"/>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AF21" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG21" s="3" t="inlineStr"/>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr"/>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr"/>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr"/>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr"/>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for women to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr"/>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="AF2" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr"/>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr"/>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr"/>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr"/>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms, Calls for women to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr"/>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr"/>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr"/>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr"/>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="AF21" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG21" s="3" t="inlineStr"/>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr"/>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr"/>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr"/>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr"/>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr"/>
@@ -9585,7 +9585,7 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr"/>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr"/>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms, Calls for women to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr"/>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr"/>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr"/>

--- a/Codebooks/Human Codebooks/content - cleaned/C - Content Analysis Codebook (cleaned) - Kally.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/C - Content Analysis Codebook (cleaned) - Kally.xlsx
@@ -450,42 +450,42 @@
   <dimension ref="A1:AG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
-    <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="28" customWidth="1" min="29" max="29"/>
-    <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Content ID</t>
@@ -5662,42 +5662,42 @@
   <dimension ref="A1:AG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
-    <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="28" customWidth="1" min="29" max="29"/>
-    <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Content ID</t>
